--- a/reports/集团总公司_现金流量表_2025-10.xlsx
+++ b/reports/集团总公司_现金流量表_2025-10.xlsx
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>204750000</v>
+        <v>204046425</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>1981200000</v>
+        <v>1979438750</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2015,10 +2015,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>4218490</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>40773525</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>2103694</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>20346883</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>1051284</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>10192172</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>844102</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>8141288</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>629044</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>6112423</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>422921</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>4073014</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>314149</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>3054282</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>211498</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>2037759</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2239,10 +2239,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>524028</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>5087752</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>265255</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>2561278</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>167039</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>1617291</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>556500</v>
+        <v>556506</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>5384800</v>
+        <v>5389914</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>3780000</v>
+        <v>3785996</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>36576000</v>
+        <v>36546450</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>209086500</v>
+        <v>219140431</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>126000000</v>
+        <v>125413991</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>1219200000</v>
+        <v>1218445881</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1408583</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>13589147</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>1049686</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>10173570</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>702378</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>6795628</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2589,10 +2589,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>526482</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>5087032</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>350075</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>3396976</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>265358</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>2557634</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>25410000</v>
+        <v>25298034</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>245872000</v>
+        <v>245919353</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2701,10 +2701,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>11760000</v>
+        <v>11817978</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>113792000</v>
+        <v>113806585</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>5355000</v>
+        <v>5328556</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>51816000</v>
+        <v>51793435</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>168525000</v>
+        <v>172161121</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>40561500</v>
+        <v>46979310</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -2913,10 +2913,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>240000</v>
+        <v>239091</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>2400000</v>
+        <v>2401020</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>2100000</v>
+        <v>2089521</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>21000000</v>
+        <v>20995103</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -2997,10 +2997,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>1280000</v>
+        <v>1286180</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>12800000</v>
+        <v>12806962</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3025,7 +3025,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>2340000</v>
+        <v>2328612</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3051,10 +3051,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>20000000</v>
+        <v>20061133</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>200000000</v>
+        <v>200193465</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2900000</v>
+        <v>2895261</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>29000000</v>
+        <v>28969946</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3107,10 +3107,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>14200000</v>
+        <v>14200581</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>142000000</v>
+        <v>142141578</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3219,10 +3219,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>520000</v>
+        <v>517501</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>5200000</v>
+        <v>5199955</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>20520000</v>
+        <v>20578634</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-18180000</v>
+        <v>-18250022</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3323,10 +3323,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>4700000</v>
+        <v>4687686</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>47000000</v>
+        <v>46952929</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3379,10 +3379,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>7500000</v>
+        <v>7503670</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>75000000</v>
+        <v>74927921</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3407,10 +3407,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>7500000</v>
+        <v>7484613</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>75000000</v>
+        <v>75058958</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3435,10 +3435,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>240000</v>
+        <v>240816</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>2400000</v>
+        <v>2398731</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>12440000</v>
+        <v>12432172</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>6100000</v>
+        <v>6130042</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>61000000</v>
+        <v>61007224</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>6100000</v>
+        <v>6069847</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>61000000</v>
+        <v>60973095</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>1000000</v>
+        <v>1004444</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>10000000</v>
+        <v>10007176</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>870000</v>
+        <v>871874</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>8700000</v>
+        <v>8708913</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>125000</v>
+        <v>124925</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>1250000</v>
+        <v>1248724</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>7225000</v>
+        <v>7259411</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3679,7 +3679,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>5215000</v>
+        <v>5172761</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -3729,7 +3729,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>27596500</v>
+        <v>33902049</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>27596500</v>
+        <v>33902049</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
